--- a/星巴克饮品菜单.xlsx
+++ b/星巴克饮品菜单.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geekest/Starbuddys/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CF2AECD-2D7C-9844-90ED-DFFEB5B2CC7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F8D562F-8644-394C-B9A5-FC618282A4BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="26560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1344,7 +1344,7 @@
     <col min="2" max="2" width="35.83203125" customWidth="1"/>
     <col min="3" max="3" width="30" customWidth="1"/>
     <col min="4" max="4" width="34" customWidth="1"/>
-    <col min="5" max="5" width="40" customWidth="1"/>
+    <col min="5" max="5" width="177.83203125" customWidth="1"/>
     <col min="6" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
     <col min="9" max="9" width="10" customWidth="1"/>
